--- a/src/route_optimizer_test/results_summary.xlsx
+++ b/src/route_optimizer_test/results_summary.xlsx
@@ -1,40 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\menon\Documents\pvrp\src\route_optimizer_test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B6C72A-8D52-4E28-9637-59C83E4B16F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+  <si>
+    <t>pos1</t>
+  </si>
+  <si>
+    <t>pos2</t>
+  </si>
+  <si>
+    <t>pos3</t>
+  </si>
+  <si>
+    <t>pos4</t>
+  </si>
+  <si>
+    <t>dist_2opt</t>
+  </si>
+  <si>
+    <t>dist_3opt</t>
+  </si>
+  <si>
+    <t>dist_2_3opt</t>
+  </si>
+  <si>
+    <t>dist_3_2opt</t>
+  </si>
+  <si>
+    <t>****************************************</t>
+  </si>
+  <si>
+    <t>total runs: 719 times</t>
+  </si>
+  <si>
+    <t>better solution: 582 times</t>
+  </si>
+  <si>
+    <t>2-3 opt is better: 75 times</t>
+  </si>
+  <si>
+    <t>3-2 opt is better: 43 times</t>
+  </si>
+  <si>
+    <t>solutions are equal: 464 times</t>
+  </si>
+  <si>
+    <t>vehicles</t>
+  </si>
+  <si>
+    <t>clients</t>
+  </si>
+  <si>
+    <t>days</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,93 +133,50 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,110 +464,630 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>pos1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>pos2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>pos3</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>pos4</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>dist_2opt</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>373</v>
-      </c>
-      <c r="C2" t="n">
-        <v>146</v>
-      </c>
-      <c r="D2" t="n">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>350</v>
+      </c>
+      <c r="C2">
+        <v>136</v>
+      </c>
+      <c r="D2">
+        <v>45</v>
+      </c>
+      <c r="E2">
+        <v>11</v>
+      </c>
+      <c r="F2">
+        <f>SUM(B2:E2)</f>
+        <v>542</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>51</v>
+      </c>
+      <c r="J2">
+        <v>2</v>
+      </c>
+      <c r="L2">
+        <f>H2*J2</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>57</v>
+      </c>
+      <c r="C3">
+        <v>43</v>
+      </c>
+      <c r="D3">
+        <v>43</v>
+      </c>
+      <c r="E3">
+        <v>35</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F5" si="0">SUM(B3:E3)</f>
+        <v>178</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>50</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L33" si="1">H3*J3</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>497</v>
+      </c>
+      <c r="C4">
+        <v>48</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>548</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>50</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5">
+        <v>446</v>
+      </c>
+      <c r="C5">
+        <v>91</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>547</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>75</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="H6">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>75</v>
+      </c>
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="H7" s="4">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>75</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>100</v>
+      </c>
+      <c r="J8">
+        <v>2</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <v>5</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>100</v>
+      </c>
+      <c r="J10">
+        <v>8</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="4">
+        <f>(75/582)*100</f>
+        <v>12.886597938144329</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
+        <v>5</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <f>(43/582)*100</f>
+        <v>7.3883161512027495</v>
+      </c>
+      <c r="H12">
+        <v>4</v>
+      </c>
+      <c r="I12">
+        <v>138</v>
+      </c>
+      <c r="J12">
+        <v>5</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="4">
+        <f>(464/582)*100</f>
+        <v>79.725085910652922</v>
+      </c>
+      <c r="H13">
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <v>163</v>
+      </c>
+      <c r="J13">
+        <v>5</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14">
+        <v>9</v>
+      </c>
+      <c r="I14">
+        <v>417</v>
+      </c>
+      <c r="J14">
+        <v>7</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="E15">
+        <f>E11+E13</f>
+        <v>92.611683848797256</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>20</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16">
+        <v>38</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>56</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H18">
+        <v>4</v>
+      </c>
+      <c r="I18">
+        <v>40</v>
+      </c>
+      <c r="J18">
+        <v>4</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H19">
+        <v>4</v>
+      </c>
+      <c r="I19">
+        <v>76</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>112</v>
+      </c>
+      <c r="J20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>184</v>
+      </c>
+      <c r="J21">
+        <v>4</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H22">
+        <v>6</v>
+      </c>
+      <c r="I22">
+        <v>60</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H23">
+        <v>6</v>
+      </c>
+      <c r="I23">
+        <v>114</v>
+      </c>
+      <c r="J23">
+        <v>4</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H24">
+        <v>6</v>
+      </c>
+      <c r="I24">
+        <v>168</v>
+      </c>
+      <c r="J24">
+        <v>4</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H25">
+        <v>3</v>
+      </c>
+      <c r="I25">
+        <v>51</v>
+      </c>
+      <c r="J25">
+        <v>6</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>dist_3opt</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>81</v>
-      </c>
-      <c r="C3" t="n">
-        <v>37</v>
-      </c>
-      <c r="D3" t="n">
+    </row>
+    <row r="26" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26">
+        <v>51</v>
+      </c>
+      <c r="J26">
+        <v>6</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H27">
+        <v>3</v>
+      </c>
+      <c r="I27">
+        <v>51</v>
+      </c>
+      <c r="J27">
+        <v>6</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="I28">
+        <v>102</v>
+      </c>
+      <c r="J28">
+        <v>6</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H29">
+        <v>6</v>
+      </c>
+      <c r="I29">
+        <v>102</v>
+      </c>
+      <c r="J29">
+        <v>6</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H30">
+        <v>6</v>
+      </c>
+      <c r="I30">
+        <v>102</v>
+      </c>
+      <c r="J30">
+        <v>6</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H31">
+        <v>9</v>
+      </c>
+      <c r="I31">
+        <v>153</v>
+      </c>
+      <c r="J31">
+        <v>6</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>dist_2_3opt</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>539</v>
-      </c>
-      <c r="C4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>dist_3_2opt</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>103</v>
-      </c>
-      <c r="C5" t="n">
-        <v>20</v>
-      </c>
-      <c r="D5" t="n">
-        <v>55</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
+    </row>
+    <row r="32" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H32">
+        <v>9</v>
+      </c>
+      <c r="I32">
+        <v>153</v>
+      </c>
+      <c r="J32">
+        <v>6</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H33">
+        <v>9</v>
+      </c>
+      <c r="I33">
+        <v>153</v>
+      </c>
+      <c r="J33">
+        <v>6</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="L34">
+        <f>SUM(L2:L33)</f>
+        <v>719</v>
       </c>
     </row>
   </sheetData>
